--- a/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65220_completo.xlsx
+++ b/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65220_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R931a9c1a747149ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R34567c1220404c6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,516 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65220_completo.xlsx
+++ b/4981_Intercuenca_Bajo_Maranon/_raw_reportes_xlsx/IDConfig_65220_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R34567c1220404c6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R28d6352a3d2d4918"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2826 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.7150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.7450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.3950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.4750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.5650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.3050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.4250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.7850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.1250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.1550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.1850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.1850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.1450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.1150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.9250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.6050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.2850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.1450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.0450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.9450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7650</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.6950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7350</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7750</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.8050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7850</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
